--- a/survey_templates/042_intermodal_transport_feedback--survey_templates.xlsx
+++ b/survey_templates/042_intermodal_transport_feedback--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>mode_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travel mode</t>
+          <t>Mode 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>origin_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Origin 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>destination</t>
+          <t>destination_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>Destination 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>transfer_time</t>
+          <t>transfer_time_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Transfer time</t>
+          <t>Transfer Time 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Transfer Number</t>
+          <t>Transfer Number (2)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>transfer_date</t>
+          <t>transfer_date_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Transfer Date</t>
+          <t>Transfer Date 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1603,7 +1603,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1637,7 +1637,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mode_choices</t>
+          <t>mode_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>origin_choices</t>
+          <t>origin_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1875,7 +1875,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>origin_choices</t>
+          <t>origin_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1892,7 +1892,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>origin_choices</t>
+          <t>origin_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>origin_choices</t>
+          <t>origin_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1994,7 +1994,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>destination_choices</t>
+          <t>destination_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>destination_choices</t>
+          <t>destination_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>destination_choices</t>
+          <t>destination_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>destination_choices</t>
+          <t>destination_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
